--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90876</v>
+        <v>90878</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90880</v>
+        <v>90881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90881</v>
+        <v>90887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90887</v>
+        <v>90891</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90891</v>
+        <v>90893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90893</v>
+        <v>90906</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90906</v>
+        <v>90908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90908</v>
+        <v>90911</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90911</v>
+        <v>90921</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136759758</v>
       </c>
       <c r="B7" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136759785</v>
       </c>
       <c r="B13" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93481</v>
+        <v>93486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93486</v>
+        <v>93488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93488</v>
+        <v>93494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90925</v>
+        <v>90930</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 40984-2026 artfynd.xlsx
+++ b/artfynd/A 40984-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858280</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858284</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858286</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858301</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136858311</v>
       </c>
       <c r="B6" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136858292</v>
       </c>
       <c r="B8" t="n">
-        <v>93494</v>
+        <v>93506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136858278</v>
       </c>
       <c r="B14" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>136858283</v>
       </c>
       <c r="B15" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136858285</v>
       </c>
       <c r="B16" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136858291</v>
       </c>
       <c r="B17" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136858294</v>
       </c>
       <c r="B18" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>136858299</v>
       </c>
       <c r="B19" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136858302</v>
       </c>
       <c r="B20" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136858300</v>
       </c>
       <c r="B23" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136858308</v>
       </c>
       <c r="B24" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136858279</v>
       </c>
       <c r="B30" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136858287</v>
       </c>
       <c r="B31" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>136858289</v>
       </c>
       <c r="B32" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136858290</v>
       </c>
       <c r="B33" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136858295</v>
       </c>
       <c r="B34" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>136858305</v>
       </c>
       <c r="B35" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>136858309</v>
       </c>
       <c r="B36" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>136858312</v>
       </c>
       <c r="B37" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136858281</v>
       </c>
       <c r="B38" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136858282</v>
       </c>
       <c r="B39" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>136858293</v>
       </c>
       <c r="B40" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136858297</v>
       </c>
       <c r="B41" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>136858304</v>
       </c>
       <c r="B42" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>136858298</v>
       </c>
       <c r="B44" t="n">
-        <v>90930</v>
+        <v>90941</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136858296</v>
       </c>
       <c r="B45" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>136858306</v>
       </c>
       <c r="B46" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136858303</v>
       </c>
       <c r="B48" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>136858310</v>
       </c>
       <c r="B49" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>136858288</v>
       </c>
       <c r="B52" t="n">
-        <v>93500</v>
+        <v>93512</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
